--- a/data/trans_orig/P37A$medicootras-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37A$medicootras-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264489</t>
+          <t>265459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524350</t>
+          <t>525739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487876</t>
+          <t>487196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495121</t>
+          <t>494909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502992</t>
+          <t>502989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986962</t>
+          <t>986861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>995970</t>
+          <t>995977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314399</t>
+          <t>314638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649414</t>
+          <t>649752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353600</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725466</t>
+          <t>725837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270811</t>
+          <t>270923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541639</t>
+          <t>541084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>610140</t>
+          <t>610283</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>632321</t>
+          <t>632303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1245419</t>
+          <t>1244659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1252299</t>
+          <t>1252294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>737524</t>
+          <t>736564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1520838</t>
+          <t>1520398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3262086</t>
+          <t>3261851</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3273636</t>
+          <t>3273564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3364117</t>
+          <t>3364585</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3375962</t>
+          <t>3375959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6630818</t>
+          <t>6630316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6647089</t>
+          <t>6646878</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289708</t>
+          <t>289153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270399</t>
+          <t>270478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284165</t>
+          <t>284087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563369</t>
+          <t>563378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577779</t>
+          <t>577990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493839</t>
+          <t>494747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516806</t>
+          <t>516778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1015338</t>
+          <t>1016527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027506</t>
+          <t>1028285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319285</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333460</t>
+          <t>333495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656713</t>
+          <t>655858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664127</t>
+          <t>664131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367129</t>
+          <t>366123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>380728</t>
+          <t>381194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751612</t>
+          <t>751965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761793</t>
+          <t>761797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213264</t>
+          <t>213297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>426079</t>
+          <t>426781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267587</t>
+          <t>266574</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270575</t>
+          <t>270456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279053</t>
+          <t>279051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541050</t>
+          <t>541641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551886</t>
+          <t>551966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>655410</t>
+          <t>655295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685501</t>
+          <t>685508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692911</t>
+          <t>692905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1344239</t>
+          <t>1343284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1354646</t>
+          <t>1354555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,82 +6472,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9282</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3923</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>17204</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8291</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>8162</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3992</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>17246</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765181</t>
+          <t>765831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777237</t>
+          <t>778042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,82 +6585,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>820715</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>814571</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>822890</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1594789</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1585747</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1599028</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>99,76%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>820715</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>815562</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>822888</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1594789</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1585705</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1598959</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3398616</t>
+          <t>3399012</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3417513</t>
+          <t>3417003</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3518473</t>
+          <t>3519927</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3541306</t>
+          <t>3541171</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6926393</t>
+          <t>6925691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6954771</t>
+          <t>6953817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288798</t>
+          <t>288625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279034</t>
+          <t>279131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>287819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572341</t>
+          <t>570609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580896</t>
+          <t>580906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492777</t>
+          <t>493091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501525</t>
+          <t>501529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516699</t>
+          <t>517626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1014203</t>
+          <t>1013963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1023596</t>
+          <t>1023595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325292</t>
+          <t>325553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334527</t>
+          <t>334564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644287</t>
+          <t>644717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653120</t>
+          <t>653058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360362</t>
+          <t>359511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368190</t>
+          <t>368202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373085</t>
+          <t>372917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384322</t>
+          <t>384231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737147</t>
+          <t>737394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>751194</t>
+          <t>750989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266222</t>
+          <t>266734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529575</t>
+          <t>529949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639206</t>
+          <t>638404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653224</t>
+          <t>653298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679425</t>
+          <t>679418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689655</t>
+          <t>689603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324747</t>
+          <t>1326356</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341509</t>
+          <t>1341990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>770834</t>
+          <t>770783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777676</t>
+          <t>777666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1596696</t>
+          <t>1597017</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1603833</t>
+          <t>1603832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362245</t>
+          <t>3362515</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3381967</t>
+          <t>3381745</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3510041</t>
+          <t>3509892</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3530642</t>
+          <t>3530016</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6880621</t>
+          <t>6880194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6908336</t>
+          <t>6907063</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>857</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311277</t>
+          <t>317988</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>310594</t>
+          <t>314742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288004</t>
+          <t>314148</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283959</t>
+          <t>310871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289463</t>
+          <t>315582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>599280</t>
+          <t>632137</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595700</t>
+          <t>627796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600740</t>
+          <t>634066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,27 +11110,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511374</t>
+          <t>523607</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498669</t>
+          <t>513280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>516294</t>
+          <t>528308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>541341</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505494</t>
+          <t>536944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512583</t>
+          <t>543936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,22 +11223,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1021273</t>
+          <t>1064949</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010361</t>
+          <t>1053136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027320</t>
+          <t>1070815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,22 +11383,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,17 +11418,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -11496,27 +11496,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>312763</t>
+          <t>312810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307759</t>
+          <t>307962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314983</t>
+          <t>314919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11531,17 +11531,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>346277</t>
+          <t>353473</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>343010</t>
+          <t>349787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348089</t>
+          <t>355258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659040</t>
+          <t>666284</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653975</t>
+          <t>661128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662451</t>
+          <t>669446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>309444</t>
+          <t>369999</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303887</t>
+          <t>364375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311721</t>
+          <t>372296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>471553</t>
+          <t>416819</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464619</t>
+          <t>408284</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474628</t>
+          <t>420217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>780996</t>
+          <t>786819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773842</t>
+          <t>778110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785371</t>
+          <t>791589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>791</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>791</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>258258</t>
+          <t>228127</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256893</t>
+          <t>226196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>437000</t>
+          <t>433791</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435510</t>
+          <t>431752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,17 +12482,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>253781</t>
+          <t>260458</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249671</t>
+          <t>256429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256068</t>
+          <t>262712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,17 +12595,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>523417</t>
+          <t>531165</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>518662</t>
+          <t>527234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525435</t>
+          <t>533247</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,22 +12755,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>27381</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -12868,27 +12868,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>618223</t>
+          <t>712134</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611901</t>
+          <t>705306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621499</t>
+          <t>716437</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>831801</t>
+          <t>752229</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>820532</t>
+          <t>742592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841960</t>
+          <t>759020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1450024</t>
+          <t>1464363</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1438633</t>
+          <t>1452027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1459289</t>
+          <t>1472896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,17 +13133,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>927641</t>
+          <t>796808</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921157</t>
+          <t>790943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13246,17 +13246,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>708909</t>
+          <t>821076</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>702921</t>
+          <t>813863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712955</t>
+          <t>825373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1636551</t>
+          <t>1617884</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1628979</t>
+          <t>1609917</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1641304</t>
+          <t>1622194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32778</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3439101</t>
+          <t>3509719</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3427039</t>
+          <t>3497577</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3447390</t>
+          <t>3518335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3668480</t>
+          <t>3687673</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3655827</t>
+          <t>3673505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3680173</t>
+          <t>3698825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7107581</t>
+          <t>7197392</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7091180</t>
+          <t>7179897</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7122307</t>
+          <t>7211772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
